--- a/People_Of_Interest_a_lot_of_threes.xlsx
+++ b/People_Of_Interest_a_lot_of_threes.xlsx
@@ -464,28 +464,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MDR_0030</t>
+          <t>RJC_0043</t>
         </is>
       </c>
       <c r="B2">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>HOMBRE</t>
+          <t>MUJER</t>
         </is>
       </c>
       <c r="D2">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>BD-I</t>
         </is>
       </c>
       <c r="G2">
@@ -498,22 +498,22 @@
         <v>3</v>
       </c>
       <c r="J2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N2">
         <v>3</v>
       </c>
       <c r="O2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P2">
         <v>3</v>
@@ -522,86 +522,86 @@
         <v>3</v>
       </c>
       <c r="R2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S2">
-        <v>0.699205898780101</v>
+        <v>0.7071067811865476</v>
       </c>
       <c r="T2">
-        <v>0.5885101980389328</v>
+        <v>0.585786437626905</v>
       </c>
       <c r="U2">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>UAM_0704</t>
+          <t>PNT_0213</t>
         </is>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>HOMBRE</t>
+          <t>MUJER</t>
         </is>
       </c>
       <c r="D3">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>BD-II</t>
         </is>
       </c>
       <c r="G3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J3">
         <v>3</v>
       </c>
       <c r="K3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N3">
         <v>3</v>
       </c>
       <c r="O3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P3">
         <v>3</v>
       </c>
       <c r="Q3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R3">
         <v>3</v>
       </c>
       <c r="S3">
-        <v>1.247219128924647</v>
+        <v>0.9189365834726815</v>
       </c>
       <c r="T3">
-        <v>0.4449944320643648</v>
+        <v>0.5211219633899049</v>
       </c>
       <c r="U3">
         <v>5</v>
@@ -610,35 +610,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CSI_0165</t>
+          <t>SVL_0019</t>
         </is>
       </c>
       <c r="B4">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>HOMBRE</t>
+          <t>MUJER</t>
         </is>
       </c>
       <c r="D4">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>BD-II</t>
         </is>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I4">
         <v>3</v>
@@ -647,55 +647,55 @@
         <v>3</v>
       </c>
       <c r="K4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N4">
         <v>3</v>
       </c>
       <c r="O4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P4">
         <v>3</v>
       </c>
       <c r="Q4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S4">
-        <v>0.4216370213557839</v>
+        <v>0.9189365834726815</v>
       </c>
       <c r="T4">
-        <v>0.7034144334862088</v>
+        <v>0.5211219633899049</v>
       </c>
       <c r="U4">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RJC_0020</t>
+          <t>RJC_0008</t>
         </is>
       </c>
       <c r="B5">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>HOMBRE</t>
+          <t>MUJER</t>
         </is>
       </c>
       <c r="D5">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -704,14 +704,14 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>SZAFF</t>
         </is>
       </c>
       <c r="G5">
         <v>1</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I5">
         <v>3</v>
@@ -720,13 +720,13 @@
         <v>1</v>
       </c>
       <c r="K5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N5">
         <v>3</v>
@@ -738,29 +738,29 @@
         <v>3</v>
       </c>
       <c r="Q5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S5">
-        <v>0.9660917830792959</v>
+        <v>1.05409255338946</v>
       </c>
       <c r="T5">
-        <v>0.5086232538105614</v>
+        <v>0.486832980505138</v>
       </c>
       <c r="U5">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>UAM_0646</t>
+          <t>RJC_0020</t>
         </is>
       </c>
       <c r="B6">
-        <v>-11</v>
+        <v>30</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -768,72 +768,72 @@
         </is>
       </c>
       <c r="D6">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SZAFF</t>
         </is>
       </c>
       <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>3</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>3</v>
+      </c>
+      <c r="L6">
+        <v>3</v>
+      </c>
+      <c r="M6">
+        <v>3</v>
+      </c>
+      <c r="N6">
+        <v>3</v>
+      </c>
+      <c r="O6">
+        <v>3</v>
+      </c>
+      <c r="P6">
+        <v>3</v>
+      </c>
+      <c r="Q6">
+        <v>3</v>
+      </c>
+      <c r="R6">
         <v>4</v>
       </c>
-      <c r="H6">
-        <v>3</v>
-      </c>
-      <c r="I6">
-        <v>3</v>
-      </c>
-      <c r="J6">
-        <v>3</v>
-      </c>
-      <c r="K6">
-        <v>3</v>
-      </c>
-      <c r="L6">
-        <v>4</v>
-      </c>
-      <c r="M6">
-        <v>3</v>
-      </c>
-      <c r="N6">
-        <v>3</v>
-      </c>
-      <c r="O6">
-        <v>3</v>
-      </c>
-      <c r="P6">
-        <v>3</v>
-      </c>
-      <c r="Q6">
-        <v>3</v>
-      </c>
-      <c r="R6">
-        <v>3</v>
-      </c>
       <c r="S6">
-        <v>0.4216370213557839</v>
+        <v>0.9660917830792959</v>
       </c>
       <c r="T6">
-        <v>0.7034144334862088</v>
+        <v>0.5086232538105614</v>
       </c>
       <c r="U6">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MDR_0218</t>
+          <t>UAM_0186</t>
         </is>
       </c>
       <c r="B7">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         </is>
       </c>
       <c r="D7">
-        <v>20</v>
+        <v>71</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -854,10 +854,10 @@
         </is>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I7">
         <v>3</v>
@@ -866,7 +866,7 @@
         <v>3</v>
       </c>
       <c r="K7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L7">
         <v>3</v>
@@ -878,7 +878,7 @@
         <v>3</v>
       </c>
       <c r="O7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P7">
         <v>3</v>
@@ -887,26 +887,26 @@
         <v>3</v>
       </c>
       <c r="R7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S7">
-        <v>1.032795558988644</v>
+        <v>0</v>
       </c>
       <c r="T7">
-        <v>0.4919333848296676</v>
+        <v>1</v>
       </c>
       <c r="U7">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>UAM_0456</t>
+          <t>UAM_0195</t>
         </is>
       </c>
       <c r="B8">
-        <v>-18</v>
+        <v>37</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="D8">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -927,16 +927,16 @@
         </is>
       </c>
       <c r="G8">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H8">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I8">
         <v>3</v>
       </c>
       <c r="J8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K8">
         <v>3</v>
@@ -945,7 +945,7 @@
         <v>3</v>
       </c>
       <c r="M8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N8">
         <v>3</v>
@@ -954,22 +954,22 @@
         <v>2</v>
       </c>
       <c r="P8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q8">
         <v>2</v>
       </c>
       <c r="R8">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S8">
-        <v>1.05934990547138</v>
+        <v>0.9486832980505138</v>
       </c>
       <c r="T8">
-        <v>0.4855901356749291</v>
+        <v>0.513167019494862</v>
       </c>
       <c r="U8">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -1048,11 +1048,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>UAM_0195</t>
+          <t>UAM_0456</t>
         </is>
       </c>
       <c r="B10">
-        <v>37</v>
+        <v>-18</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="D10">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1073,16 +1073,16 @@
         </is>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H10">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I10">
         <v>3</v>
       </c>
       <c r="J10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K10">
         <v>3</v>
@@ -1091,7 +1091,7 @@
         <v>3</v>
       </c>
       <c r="M10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N10">
         <v>3</v>
@@ -1100,22 +1100,22 @@
         <v>2</v>
       </c>
       <c r="P10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q10">
         <v>2</v>
       </c>
       <c r="R10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S10">
-        <v>0.9486832980505138</v>
+        <v>1.05934990547138</v>
       </c>
       <c r="T10">
-        <v>0.513167019494862</v>
+        <v>0.4855901356749291</v>
       </c>
       <c r="U10">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -1194,32 +1194,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SVL_0019</t>
+          <t>UAM_0646</t>
         </is>
       </c>
       <c r="B12">
-        <v>44</v>
+        <v>-11</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MUJER</t>
+          <t>HOMBRE</t>
         </is>
       </c>
       <c r="D12">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>BD-II</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G12">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H12">
         <v>3</v>
@@ -1231,107 +1231,107 @@
         <v>3</v>
       </c>
       <c r="K12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L12">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N12">
         <v>3</v>
       </c>
       <c r="O12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P12">
         <v>3</v>
       </c>
       <c r="Q12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R12">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S12">
-        <v>0.9189365834726815</v>
+        <v>0.4216370213557839</v>
       </c>
       <c r="T12">
-        <v>0.5211219633899049</v>
+        <v>0.7034144334862088</v>
       </c>
       <c r="U12">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PNT_0213</t>
+          <t>UAM_0704</t>
         </is>
       </c>
       <c r="B13">
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MUJER</t>
+          <t>HOMBRE</t>
         </is>
       </c>
       <c r="D13">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>BD-II</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J13">
         <v>3</v>
       </c>
       <c r="K13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N13">
         <v>3</v>
       </c>
       <c r="O13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P13">
         <v>3</v>
       </c>
       <c r="Q13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R13">
         <v>3</v>
       </c>
       <c r="S13">
-        <v>0.9189365834726815</v>
+        <v>1.247219128924647</v>
       </c>
       <c r="T13">
-        <v>0.5211219633899049</v>
+        <v>0.4449944320643648</v>
       </c>
       <c r="U13">
         <v>5</v>
@@ -1340,32 +1340,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>RJC_0043</t>
+          <t>CSI_0165</t>
         </is>
       </c>
       <c r="B14">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MUJER</t>
+          <t>HOMBRE</t>
         </is>
       </c>
       <c r="D14">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>BD-I</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H14">
         <v>2</v>
@@ -1380,10 +1380,10 @@
         <v>3</v>
       </c>
       <c r="L14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N14">
         <v>3</v>
@@ -1395,89 +1395,89 @@
         <v>3</v>
       </c>
       <c r="Q14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S14">
-        <v>0.7071067811865476</v>
+        <v>0.4216370213557839</v>
       </c>
       <c r="T14">
-        <v>0.585786437626905</v>
+        <v>0.7034144334862088</v>
       </c>
       <c r="U14">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>RJC_0008</t>
+          <t>MDR_0030</t>
         </is>
       </c>
       <c r="B15">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MUJER</t>
+          <t>HOMBRE</t>
         </is>
       </c>
       <c r="D15">
-        <v>71</v>
+        <v>19</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G15">
         <v>1</v>
       </c>
       <c r="H15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I15">
         <v>3</v>
       </c>
       <c r="J15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N15">
         <v>3</v>
       </c>
       <c r="O15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P15">
         <v>3</v>
       </c>
       <c r="Q15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S15">
-        <v>1.05409255338946</v>
+        <v>0.699205898780101</v>
       </c>
       <c r="T15">
-        <v>0.486832980505138</v>
+        <v>0.5885101980389328</v>
       </c>
       <c r="U15">
         <v>5</v>
@@ -1486,11 +1486,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>UAM_0186</t>
+          <t>MDR_0218</t>
         </is>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         </is>
       </c>
       <c r="D16">
-        <v>71</v>
+        <v>20</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1511,10 +1511,10 @@
         </is>
       </c>
       <c r="G16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I16">
         <v>3</v>
@@ -1523,7 +1523,7 @@
         <v>3</v>
       </c>
       <c r="K16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L16">
         <v>3</v>
@@ -1535,7 +1535,7 @@
         <v>3</v>
       </c>
       <c r="O16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P16">
         <v>3</v>
@@ -1544,16 +1544,16 @@
         <v>3</v>
       </c>
       <c r="R16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.032795558988644</v>
       </c>
       <c r="T16">
-        <v>1</v>
+        <v>0.4919333848296676</v>
       </c>
       <c r="U16">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/People_Of_Interest_a_lot_of_threes.xlsx
+++ b/People_Of_Interest_a_lot_of_threes.xlsx
@@ -464,11 +464,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>RJC_0043</t>
+          <t>PNT_0213</t>
         </is>
       </c>
       <c r="B2">
-        <v>29</v>
+        <v>-12</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -476,7 +476,7 @@
         </is>
       </c>
       <c r="D2">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -485,14 +485,14 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>BD-I</t>
+          <t>BD-II</t>
         </is>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I2">
         <v>3</v>
@@ -501,13 +501,13 @@
         <v>3</v>
       </c>
       <c r="K2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N2">
         <v>3</v>
@@ -525,23 +525,23 @@
         <v>3</v>
       </c>
       <c r="S2">
-        <v>0.7071067811865476</v>
+        <v>0.9189365834726815</v>
       </c>
       <c r="T2">
-        <v>0.585786437626905</v>
+        <v>0.5211219633899049</v>
       </c>
       <c r="U2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PNT_0213</t>
+          <t>RJC_0008</t>
         </is>
       </c>
       <c r="B3">
-        <v>-12</v>
+        <v>50</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
         </is>
       </c>
       <c r="D3">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -558,29 +558,29 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>BD-II</t>
+          <t>SZAFF</t>
         </is>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I3">
         <v>3</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L3">
         <v>1</v>
       </c>
       <c r="M3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N3">
         <v>3</v>
@@ -592,16 +592,16 @@
         <v>3</v>
       </c>
       <c r="Q3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S3">
-        <v>0.9189365834726815</v>
+        <v>1.05409255338946</v>
       </c>
       <c r="T3">
-        <v>0.5211219633899049</v>
+        <v>0.486832980505138</v>
       </c>
       <c r="U3">
         <v>5</v>
@@ -610,19 +610,19 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SVL_0019</t>
+          <t>RJC_0020</t>
         </is>
       </c>
       <c r="B4">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MUJER</t>
+          <t>HOMBRE</t>
         </is>
       </c>
       <c r="D4">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -631,63 +631,63 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>BD-II</t>
+          <t>SZAFF</t>
         </is>
       </c>
       <c r="G4">
         <v>1</v>
       </c>
       <c r="H4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I4">
         <v>3</v>
       </c>
       <c r="J4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N4">
         <v>3</v>
       </c>
       <c r="O4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P4">
         <v>3</v>
       </c>
       <c r="Q4">
+        <v>3</v>
+      </c>
+      <c r="R4">
         <v>4</v>
       </c>
-      <c r="R4">
-        <v>5</v>
-      </c>
       <c r="S4">
-        <v>0.9189365834726815</v>
+        <v>0.9660917830792959</v>
       </c>
       <c r="T4">
-        <v>0.5211219633899049</v>
+        <v>0.5086232538105614</v>
       </c>
       <c r="U4">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RJC_0008</t>
+          <t>RJC_0043</t>
         </is>
       </c>
       <c r="B5">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="D5">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -704,29 +704,29 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>SZAFF</t>
+          <t>BD-I</t>
         </is>
       </c>
       <c r="G5">
         <v>1</v>
       </c>
       <c r="H5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I5">
         <v>3</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N5">
         <v>3</v>
@@ -738,37 +738,37 @@
         <v>3</v>
       </c>
       <c r="Q5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S5">
-        <v>1.05409255338946</v>
+        <v>0.7071067811865476</v>
       </c>
       <c r="T5">
-        <v>0.486832980505138</v>
+        <v>0.585786437626905</v>
       </c>
       <c r="U5">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>RJC_0020</t>
+          <t>SVL_0019</t>
         </is>
       </c>
       <c r="B6">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>HOMBRE</t>
+          <t>MUJER</t>
         </is>
       </c>
       <c r="D6">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -777,53 +777,53 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>SZAFF</t>
+          <t>BD-II</t>
         </is>
       </c>
       <c r="G6">
         <v>1</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I6">
         <v>3</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N6">
         <v>3</v>
       </c>
       <c r="O6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P6">
         <v>3</v>
       </c>
       <c r="Q6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S6">
-        <v>0.9660917830792959</v>
+        <v>0.9189365834726815</v>
       </c>
       <c r="T6">
-        <v>0.5086232538105614</v>
+        <v>0.5211219633899049</v>
       </c>
       <c r="U6">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
